--- a/slide_classification/TCGA_Results/TITAN/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/TITAN/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -761,10 +761,10 @@
         <v>0.8482142857142857</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8910891089108911</v>
+        <v>0.8811881188118812</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8694670257156476</v>
+        <v>0.8669917781908951</v>
       </c>
     </row>
     <row r="15">
@@ -783,10 +783,10 @@
         <v>0.5945652173913043</v>
       </c>
       <c r="E15" t="n">
-        <v>0.649812734082397</v>
+        <v>0.6081460674157304</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6284448458437834</v>
+        <v>0.6180281791771167</v>
       </c>
     </row>
     <row r="16">
@@ -805,10 +805,10 @@
         <v>0.617286432160804</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6804716709807306</v>
+        <v>0.6340579710144928</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6524443444619092</v>
+        <v>0.6408409194703498</v>
       </c>
     </row>
     <row r="17">
@@ -827,10 +827,10 @@
         <v>0.8083991385498923</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8782465822078326</v>
+        <v>0.8633232888506243</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8476531303671632</v>
+        <v>0.8439223070278611</v>
       </c>
     </row>
     <row r="18">
@@ -840,19 +840,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7988636363636363</v>
+        <v>0.7647727272727272</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6442307692307693</v>
+        <v>0.6391941391941393</v>
       </c>
       <c r="D18" t="n">
         <v>0.8445652173913044</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7818352059925093</v>
+        <v>0.7771535580524345</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7673737072445548</v>
+        <v>0.7564214104776512</v>
       </c>
     </row>
     <row r="19">
@@ -878,7 +878,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[[86, 3], [8, 4]]</t>
+          <t>[[86, 3], [9, 3]]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1406,34 +1406,34 @@
         <v>413</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8694670257156476</v>
+        <v>0.8669917781908951</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02271420690823589</v>
+        <v>0.02067064901202896</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6284448458437834</v>
+        <v>0.6180281791771167</v>
       </c>
       <c r="I4" t="n">
-        <v>0.061228298141221</v>
+        <v>0.06024334808341189</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6524443444619092</v>
+        <v>0.6408409194703498</v>
       </c>
       <c r="K4" t="n">
-        <v>0.069946959685739</v>
+        <v>0.06816208346238001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8476531303671632</v>
+        <v>0.8439223070278611</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03378009961121454</v>
+        <v>0.03089619280424132</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7673737072445548</v>
+        <v>0.7564214104776512</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07470519226159023</v>
+        <v>0.07418074255675086</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>

--- a/slide_classification/TCGA_Results/TITAN/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/TITAN/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -610,19 +610,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7961165048543689</v>
+        <v>0.8446601941747572</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8350515463917526</v>
+        <v>0.8556701030927835</v>
       </c>
       <c r="D8" t="n">
         <v>0.7946428571428571</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7821782178217822</v>
+        <v>0.8217821782178217</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8019972815526901</v>
+        <v>0.8291888331570548</v>
       </c>
     </row>
     <row r="9">
@@ -632,19 +632,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8253787878787879</v>
+        <v>0.8537878787878788</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7422161172161172</v>
+        <v>0.7866300366300366</v>
       </c>
       <c r="D9" t="n">
         <v>0.816304347826087</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6961610486891385</v>
+        <v>0.7546816479400749</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7700150754025327</v>
+        <v>0.8028509777960193</v>
       </c>
     </row>
     <row r="10">
@@ -654,19 +654,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7105580088317944</v>
+        <v>0.7607433217189314</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7006172839506173</v>
+        <v>0.7380401234567902</v>
       </c>
       <c r="D10" t="n">
         <v>0.7293833385859859</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6281793842034806</v>
+        <v>0.6817226890756303</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6921845038929695</v>
+        <v>0.7274723682093345</v>
       </c>
     </row>
     <row r="11">
@@ -676,19 +676,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8220896197183647</v>
+        <v>0.8611684313791822</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8474608629247805</v>
+        <v>0.8665282550591829</v>
       </c>
       <c r="D11" t="n">
         <v>0.8148139810604356</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8106087717205457</v>
+        <v>0.842686579582328</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8237433088560315</v>
+        <v>0.8462993117702822</v>
       </c>
     </row>
     <row r="12">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9204545454545454</v>
+        <v>0.9181818181818182</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8177655677655677</v>
+        <v>0.8663003663003662</v>
       </c>
       <c r="D12" t="n">
         <v>0.8581521739130434</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8220973782771536</v>
+        <v>0.8155430711610486</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8546174163525775</v>
+        <v>0.8645443573890691</v>
       </c>
     </row>
     <row r="13">
@@ -721,12 +721,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[69, 19], [2, 13]]</t>
+          <t>[[74, 14], [2, 13]]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[73, 11], [5, 8]]</t>
+          <t>[[74, 10], [4, 9]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[72, 17], [5, 7]]</t>
+          <t>[[75, 14], [4, 8]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[72, 17], [4, 11]]</t>
+          <t>[[74, 14], [3, 12]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8019972815526901</v>
+        <v>0.8291888331570548</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01983715456029504</v>
+        <v>0.02339286037080223</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7700150754025327</v>
+        <v>0.8028509777960193</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0534673656043766</v>
+        <v>0.03660247368314561</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6921845038929695</v>
+        <v>0.7274723682093345</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03837025577260935</v>
+        <v>0.02878940233412817</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8237433088560315</v>
+        <v>0.8462993117702822</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01429603108744458</v>
+        <v>0.02021558030517319</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8546174163525775</v>
+        <v>0.8645443573890691</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04111761696678012</v>
+        <v>0.03647617999867111</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[72, 17], [4, 11]]</t>
+          <t>[[74, 14], [3, 12]]</t>
         </is>
       </c>
     </row>
